--- a/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACCD9E9B-9E98-440C-89BD-4FC1236B3DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9F5A5B-08E5-420A-B570-21609B0C3B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1872,7 +1872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA28451-17AD-49BA-81E4-07511433EE6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B89249-A0F7-4B53-B800-F02C01B7CC80}">
   <dimension ref="B2:AE204"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9F5A5B-08E5-420A-B570-21609B0C3B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E3CA3F1-7E3A-40BF-9CAE-17C3E2B6191A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1872,7 +1872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B89249-A0F7-4B53-B800-F02C01B7CC80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3BF75E2-5242-4517-B302-71CCED6E81F3}">
   <dimension ref="B2:AE204"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E3CA3F1-7E3A-40BF-9CAE-17C3E2B6191A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF5B82E-BD69-4106-AC60-52B2769483CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="423">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1386,7 +1386,13 @@
     <t>pset_set</t>
   </si>
   <si>
-    <t>ELE,DMD,PRE</t>
+    <t>STGOUT_BND</t>
+  </si>
+  <si>
+    <t>DMD,PRE,ELE</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
 </sst>
 </file>
@@ -1873,10 +1879,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3BF75E2-5242-4517-B302-71CCED6E81F3}">
-  <dimension ref="B2:AE204"/>
+  <dimension ref="B2:AF204"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -1943,7 +1949,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -2005,10 +2011,13 @@
         <v>418</v>
       </c>
       <c r="AE4" t="s">
+        <v>420</v>
+      </c>
+      <c r="AF4" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>96</v>
       </c>
@@ -2069,11 +2078,11 @@
       <c r="AD5">
         <v>0</v>
       </c>
-      <c r="AE5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AF5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>97</v>
       </c>
@@ -2122,8 +2131,23 @@
       <c r="X6" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="7" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AA6" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>98</v>
       </c>
@@ -2173,7 +2197,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>99</v>
       </c>
@@ -2223,7 +2247,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>100</v>
       </c>
@@ -2273,7 +2297,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>101</v>
       </c>
@@ -2323,7 +2347,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>102</v>
       </c>
@@ -2373,7 +2397,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>103</v>
       </c>
@@ -2423,7 +2447,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>104</v>
       </c>
@@ -2473,7 +2497,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>105</v>
       </c>
@@ -2523,7 +2547,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>106</v>
       </c>
@@ -2573,7 +2597,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>107</v>
       </c>

--- a/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4BAB1B1-EBAA-4BF5-85CB-8C3D901E5A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6053E5DC-A183-44E2-9D59-E849B476F0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -7505,28 +7505,28 @@
         <v>121</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
@@ -7585,11 +7585,11 @@
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -7615,11 +7615,11 @@
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -7645,11 +7645,11 @@
       </c>
       <c r="F22">
         <f>G11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <f>H11</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -7675,11 +7675,11 @@
       </c>
       <c r="F23">
         <f>I11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>4</v>
